--- a/Dashboard_Revenue_Assurance_Consolidado.xlsx
+++ b/Dashboard_Revenue_Assurance_Consolidado.xlsx
@@ -10,7 +10,7 @@
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="5" documentId="11_5963697DF4C0106AA63241150627E56E5A49D655" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D00D9803-67CB-452B-BAE9-6E0C9B118435}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="2" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="01_Pareto_Cliente" sheetId="1" r:id="rId1"/>
